--- a/public/PTL_Import_Sheet.xlsx
+++ b/public/PTL_Import_Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitin\PTL\apis\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66DE33D-6B2F-489A-81A8-E4A1896A3D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F97EC1-A5B6-48EE-948E-FAFE0082CFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{21EC4B72-9BFB-4243-AE41-2F370EDEFE60}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>GSM</t>
   </si>
@@ -78,21 +78,6 @@
   </si>
   <si>
     <t>pkt_grs</t>
-  </si>
-  <si>
-    <t>3M PEARL WHITE GB</t>
-  </si>
-  <si>
-    <t>GN 2</t>
-  </si>
-  <si>
-    <t>A-35</t>
-  </si>
-  <si>
-    <t>GREY BACKs</t>
-  </si>
-  <si>
-    <t>GREY BACKss</t>
   </si>
 </sst>
 </file>
@@ -444,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67693A6-3809-475D-B302-210289A041AA}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -505,100 +490,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
-      <c r="K2">
-        <v>10</v>
-      </c>
-      <c r="L2">
-        <v>100</v>
-      </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>14</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>16</v>
-      </c>
-      <c r="H3">
-        <v>17</v>
-      </c>
-      <c r="I3">
-        <v>18</v>
-      </c>
-      <c r="J3">
-        <v>19</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>110</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
